--- a/backend/data/raw/Mayes_Bowling_Batting.xlsx
+++ b/backend/data/raw/Mayes_Bowling_Batting.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T216"/>
+  <dimension ref="A1:T234"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="20.44140625" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -21073,6 +21073,1591 @@
         </is>
       </c>
     </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Hollywoodbets Dolphins</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>B Parsons</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="K217" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>Leg Stump</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O217" t="n">
+        <v>1</v>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Leg Bye</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>Cover</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>Back Foot Flick</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Hollywoodbets Dolphins</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>R Pillay</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K218" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>Wide</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="O218" t="n">
+        <v>0</v>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>Cut</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Hollywoodbets Dolphins</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>R Pillay</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K219" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="O219" t="n">
+        <v>0</v>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>Off Drive</t>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Hollywoodbets Dolphins</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>R Pillay</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K220" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>Off Stump</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O220" t="n">
+        <v>0</v>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Hollywoodbets Dolphins</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>R Pillay</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K221" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>Leg Stump</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O221" t="n">
+        <v>1</v>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>Mid On</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>Pull</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Hollywoodbets Dolphins</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>B Parsons</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="K222" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O222" t="n">
+        <v>0</v>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>Cover Drive</t>
+        </is>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Hollywoodbets Dolphins</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>J Smith</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K223" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O223" t="n">
+        <v>0</v>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>Front Foot Defense</t>
+        </is>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Hollywoodbets Dolphins</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>J Smith</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K224" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O224" t="n">
+        <v>1</v>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>Front Foot Defense</t>
+        </is>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Hollywoodbets Dolphins</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>R Pillay</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K225" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>Off Stump</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="O225" t="n">
+        <v>1</v>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>Off Drive</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Hollywoodbets Dolphins</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>J Smith</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K226" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>Leg Stump</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O226" t="n">
+        <v>0</v>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>Pull</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Hollywoodbets Dolphins</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>J Smith</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K227" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>Wicket</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>Caught</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>Extra Cover</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>Cover Drive</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>Caught at Extra Cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Hollywoodbets Dolphins</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>H Viljoen</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K228" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O228" t="n">
+        <v>0</v>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>Back Foot Defense</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Hollywoodbets Dolphins</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>H Viljoen</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K229" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>Middle Stump</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O229" t="n">
+        <v>0</v>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>Back Foot Defense</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Hollywoodbets Dolphins</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>H Viljoen</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K230" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="O230" t="n">
+        <v>1</v>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>On Drive</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Hollywoodbets Dolphins</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>R Pillay</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K231" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>Middle Stump</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="O231" t="n">
+        <v>1</v>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>Square Leg</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>Pull</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Hollywoodbets Dolphins</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>H Viljoen</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K232" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O232" t="n">
+        <v>1</v>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>Third Man</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Hollywoodbets Dolphins</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>R Pillay</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K233" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>Middle Stump</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>Yorker</t>
+        </is>
+      </c>
+      <c r="O233" t="n">
+        <v>0</v>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>Dig Out</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Hollywoodbets Dolphins</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>R Pillay</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K234" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>Middle Stump</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="O234" t="n">
+        <v>4</v>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>Mid On</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>Lofted On Drive</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:S191">
     <sortState ref="A2:S191">
@@ -21089,7 +22674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:Q77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="20.44140625" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -27038,6 +28623,156 @@
         </is>
       </c>
       <c r="Q75" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Hollywoodbets Dolphins</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>7</v>
+      </c>
+      <c r="I76" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>T Luus</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Wide</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Cut</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Hollywoodbets Dolphins</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>7</v>
+      </c>
+      <c r="I77" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>T Luus</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Leg Stump</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Flick</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Wicket</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>LBW</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
         <is>
           <t>Miss</t>
         </is>

--- a/backend/data/raw/Mayes_Bowling_Batting.xlsx
+++ b/backend/data/raw/Mayes_Bowling_Batting.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T234"/>
+  <dimension ref="A1:T258"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="20.44140625" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -22653,6 +22653,2167 @@
         </is>
       </c>
       <c r="S234" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Northern Cape Heat</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Kimberley Oval</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>S Stolk</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K235" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="O235" t="n">
+        <v>1</v>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>Third Man</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>Guide</t>
+        </is>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Northern Cape Heat</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Kimberley Oval</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>L Doherty</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K236" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>Leg Stump</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O236" t="n">
+        <v>1</v>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>Square Leg</t>
+        </is>
+      </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>Back Foot Punch</t>
+        </is>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Northern Cape Heat</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Kimberley Oval</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>S Stolk</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K237" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>Off Stump</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O237" t="n">
+        <v>4</v>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>Third Man</t>
+        </is>
+      </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>Back Foot Defense</t>
+        </is>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Northern Cape Heat</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Kimberley Oval</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>S Stolk</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K238" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>Wide</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="O238" t="n">
+        <v>1</v>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>Cut</t>
+        </is>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Northern Cape Heat</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Kimberley Oval</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>L Doherty</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K239" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O239" t="n">
+        <v>0</v>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t>Back Foot Defense</t>
+        </is>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Northern Cape Heat</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Kimberley Oval</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>L Doherty</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K240" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>Wide</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="O240" t="n">
+        <v>1</v>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>Mid Off</t>
+        </is>
+      </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>Off Drive</t>
+        </is>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Northern Cape Heat</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Kimberley Oval</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>L Doherty</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K241" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O241" t="n">
+        <v>1</v>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>Cover Drive</t>
+        </is>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Northern Cape Heat</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Kimberley Oval</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>S Stolk</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K242" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>Outside Leg</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O242" t="n">
+        <v>0</v>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>Front Foot Defense</t>
+        </is>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Northern Cape Heat</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Kimberley Oval</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>S Stolk</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K243" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O243" t="n">
+        <v>5</v>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>Cover</t>
+        </is>
+      </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>Front Foot Defense</t>
+        </is>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Northern Cape Heat</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Kimberley Oval</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>L Doherty</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K244" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="O244" t="n">
+        <v>0</v>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>Cover Drive</t>
+        </is>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Northern Cape Heat</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Kimberley Oval</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>L Doherty</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K245" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="O245" t="n">
+        <v>0</v>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t>Cover Drive</t>
+        </is>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Northern Cape Heat</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Kimberley Oval</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>L Doherty</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K246" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>Outside Leg</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="O246" t="n">
+        <v>1</v>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>Fine Leg</t>
+        </is>
+      </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>Back Foot Flick</t>
+        </is>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Northern Cape Heat</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Kimberley Oval</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>S Stolk</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K247" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>Off Stump</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="O247" t="n">
+        <v>2</v>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>Cow Corner</t>
+        </is>
+      </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>Back Foot Flick</t>
+        </is>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Northern Cape Heat</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Kimberley Oval</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>S Stolk</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K248" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>Leg Stump</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="O248" t="n">
+        <v>1</v>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>Square Leg</t>
+        </is>
+      </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t>Pull</t>
+        </is>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Northern Cape Heat</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Kimberley Oval</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>N Yikha</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K249" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="O249" t="n">
+        <v>0</v>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>Cut</t>
+        </is>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Northern Cape Heat</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Kimberley Oval</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>N Yikha</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K250" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>Middle Stump</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>Yorker</t>
+        </is>
+      </c>
+      <c r="O250" t="n">
+        <v>1</v>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>Cover</t>
+        </is>
+      </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>Dig Out</t>
+        </is>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Northern Cape Heat</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Kimberley Oval</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>S Stolk</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K251" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>Middle Stump</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="O251" t="n">
+        <v>6</v>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>Mid Wicket</t>
+        </is>
+      </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>Pull</t>
+        </is>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Northern Cape Heat</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Kimberley Oval</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>S Stolk</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K252" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="O252" t="n">
+        <v>6</v>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>Extra Cover</t>
+        </is>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>Lofted Cover Drive</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Northern Cape Heat</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Kimberley Oval</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>K Jacobs</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K253" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="O253" t="n">
+        <v>1</v>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>Cow Corner</t>
+        </is>
+      </c>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t>Pull</t>
+        </is>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Northern Cape Heat</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Kimberley Oval</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>T Isaac</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="K254" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>Around</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="O254" t="n">
+        <v>1</v>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>Pull</t>
+        </is>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Northern Cape Heat</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Kimberley Oval</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>K Jacobs</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K255" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>Off Stump</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>Wicket</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>Caught</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>Keeper</t>
+        </is>
+      </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t>Reverse Scoop</t>
+        </is>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Northern Cape Heat</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Kimberley Oval</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>T Ntuli</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K256" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>Outside Leg</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="O256" t="n">
+        <v>1</v>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>Square Leg</t>
+        </is>
+      </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>Pull</t>
+        </is>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Northern Cape Heat</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Kimberley Oval</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>T Isaac</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="K257" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>Around</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>Outside Leg</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="O257" t="n">
+        <v>1</v>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>Fine Leg</t>
+        </is>
+      </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>Pull</t>
+        </is>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Northern Cape Heat</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Kimberley Oval</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>T Ntuli</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K258" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>Middle Stump</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="O258" t="n">
+        <v>2</v>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>Mid Wicket</t>
+        </is>
+      </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="S258" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>

--- a/backend/data/raw/Mayes_Bowling_Batting.xlsx
+++ b/backend/data/raw/Mayes_Bowling_Batting.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T258"/>
+  <dimension ref="A1:T284"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="20.44140625" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -24819,6 +24819,2319 @@
         </is>
       </c>
     </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>N Engelbrecht</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="K259" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="O259" t="n">
+        <v>1</v>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>Cut</t>
+        </is>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>J Malan</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K260" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O260" t="n">
+        <v>0</v>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t>Front Foot Defense</t>
+        </is>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>J Malan</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K261" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>Leg Stump</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O261" t="n">
+        <v>0</v>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>Back Foot Flick</t>
+        </is>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>J Malan</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K262" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>Outside Leg</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="O262" t="n">
+        <v>0</v>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>Pull</t>
+        </is>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>J Malan</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K263" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>Wide</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O263" t="n">
+        <v>0</v>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t>Cover Drive</t>
+        </is>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>J Malan</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K264" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>Wide</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="O264" t="n">
+        <v>1</v>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>Mid On</t>
+        </is>
+      </c>
+      <c r="R264" t="inlineStr">
+        <is>
+          <t>Cover Drive</t>
+        </is>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>J Malan</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K265" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>Leg Stump</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="O265" t="n">
+        <v>1</v>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>Square Leg</t>
+        </is>
+      </c>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>Pull</t>
+        </is>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>N Engelbrecht</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="K266" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>Off Stump</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O266" t="n">
+        <v>1</v>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="R266" t="inlineStr">
+        <is>
+          <t>Back Foot Punch</t>
+        </is>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>J Malan</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K267" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O267" t="n">
+        <v>1</v>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="R267" t="inlineStr">
+        <is>
+          <t>Back Foot Drive</t>
+        </is>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>N Engelbrecht</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="K268" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="O268" t="n">
+        <v>4</v>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>Cover</t>
+        </is>
+      </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t>Cover Drive</t>
+        </is>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>N Engelbrecht</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="K269" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>Wide</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="O269" t="n">
+        <v>1</v>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>Wide</t>
+        </is>
+      </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>Cover Drive</t>
+        </is>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>N Engelbrecht</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="K270" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="O270" t="n">
+        <v>1</v>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>Cover</t>
+        </is>
+      </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>Cover Drive</t>
+        </is>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>End 2</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>J Malan</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K271" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O271" t="n">
+        <v>0</v>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>Cover Drive</t>
+        </is>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>J Malan</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K272" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>Outside Leg</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="O272" t="n">
+        <v>1</v>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>Wide</t>
+        </is>
+      </c>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>Leave</t>
+        </is>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>Leave</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>J Malan</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K273" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>Off Stump</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O273" t="n">
+        <v>0</v>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>Cut</t>
+        </is>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>J Malan</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K274" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>Off Stump</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O274" t="n">
+        <v>0</v>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R274" t="inlineStr">
+        <is>
+          <t>Cut</t>
+        </is>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>J Malan</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K275" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>Off Stump</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O275" t="n">
+        <v>4</v>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>Fine Leg</t>
+        </is>
+      </c>
+      <c r="R275" t="inlineStr">
+        <is>
+          <t>Back Foot Defense</t>
+        </is>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>J Malan</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K276" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O276" t="n">
+        <v>0</v>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>Cut</t>
+        </is>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>J Malan</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K277" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>Middle Stump</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>Yorker</t>
+        </is>
+      </c>
+      <c r="O277" t="n">
+        <v>1</v>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>Mid On</t>
+        </is>
+      </c>
+      <c r="R277" t="inlineStr">
+        <is>
+          <t>Dig Out</t>
+        </is>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>S Van Staden</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K278" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>Leg Stump</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O278" t="n">
+        <v>1</v>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>Square Leg</t>
+        </is>
+      </c>
+      <c r="R278" t="inlineStr">
+        <is>
+          <t>Back Foot Defense</t>
+        </is>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>R Coetzee</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K279" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>Leg Stump</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>Yorker</t>
+        </is>
+      </c>
+      <c r="O279" t="n">
+        <v>1</v>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>Square Leg</t>
+        </is>
+      </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>Leg Glance</t>
+        </is>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>P Moletsane</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K280" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>Leg Stump</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="O280" t="n">
+        <v>2</v>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>Mid Wicket</t>
+        </is>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>Back Foot Defense</t>
+        </is>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>P Moletsane</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K281" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>Wide</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="O281" t="n">
+        <v>1</v>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>Mid Wicket</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>Cover Drive</t>
+        </is>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>R Coetzee</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K282" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>Off Stump</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="O282" t="n">
+        <v>1</v>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="R282" t="inlineStr">
+        <is>
+          <t>Cut</t>
+        </is>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>P Moletsane</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K283" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>Middle Stump</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="O283" t="n">
+        <v>1</v>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>Square Leg</t>
+        </is>
+      </c>
+      <c r="R283" t="inlineStr">
+        <is>
+          <t>Pull</t>
+        </is>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>End 1</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>R Coetzee</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="K284" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>Leg Stump</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>Wicket</t>
+        </is>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>Bowled</t>
+        </is>
+      </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:S191">
     <sortState ref="A2:S191">
@@ -24835,7 +27148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:R95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="20.44140625" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -24908,35 +27221,40 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>Bowler Type</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Length</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Shot</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Type of Run</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Area Scored</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>contact/miss/leave</t>
         </is>
@@ -24987,35 +27305,35 @@
           <t>H Coetzer</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Off Stump</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>On Drive</t>
         </is>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>1</v>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Point</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -25066,35 +27384,35 @@
           <t>A Mhletywa</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Outside Leg</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Leg Glance</t>
         </is>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>1</v>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Square Leg</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -25145,35 +27463,35 @@
           <t>A Mhletywa</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Outside Leg</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Leg Glance</t>
         </is>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>1</v>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Fine Leg</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -25224,35 +27542,35 @@
           <t>H Coetzer</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Off Stump</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Off Drive</t>
         </is>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>1</v>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Mid Wicket</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -25303,35 +27621,35 @@
           <t>A Mhletywa</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Leg Stump</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Leg Glance</t>
         </is>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>1</v>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Square Leg</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -25382,35 +27700,35 @@
           <t>A Mhletywa</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Middle Stump</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Off Drive</t>
         </is>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -25461,35 +27779,35 @@
           <t>A Mhletywa</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Leg Stump</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Yorker</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>On Drive</t>
         </is>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -25540,35 +27858,35 @@
           <t>A Mhletywa</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Middle Stump</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Forward Defence</t>
         </is>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>1</v>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Cover</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -25619,35 +27937,35 @@
           <t>S Langa</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Leg Stump</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Back Foot Defense</t>
         </is>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -25698,35 +28016,35 @@
           <t>S Langa</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Leg Stump</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Flick</t>
         </is>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>N/a</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -25777,35 +28095,35 @@
           <t>S Langa</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -25856,35 +28174,35 @@
           <t>S Langa</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Forward Defence</t>
         </is>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>1</v>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Point</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -25935,35 +28253,35 @@
           <t>A Mhletywa</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Hook</t>
         </is>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>4</v>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Cow Corner</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -26014,35 +28332,35 @@
           <t>A Mhletywa</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Leg Stump</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>On Drive</t>
         </is>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>1</v>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Mid On</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -26093,35 +28411,35 @@
           <t>A Mhletywa</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Yorker</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Dig Out</t>
         </is>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -26172,35 +28490,35 @@
           <t>S Langa</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Leg Stump</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Leg Glance</t>
         </is>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>1</v>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Square Leg</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -26251,35 +28569,35 @@
           <t>S Langa</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Off Stump</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Yorker</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Dig Out</t>
         </is>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -26330,35 +28648,35 @@
           <t>S Langa</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>Outside Leg</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Flick</t>
         </is>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>4</v>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Fine Leg</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -26409,35 +28727,35 @@
           <t>S Langa</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>Wide</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Cut</t>
         </is>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>4</v>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Point</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -26488,35 +28806,35 @@
           <t>T Ntini</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Forward Defence</t>
         </is>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -26567,35 +28885,35 @@
           <t>T Ntini</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>Middle Stump</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>On Drive</t>
         </is>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>1</v>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
           <t>Mid On</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -26646,35 +28964,35 @@
           <t>S Langa</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Outside Leg</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Pull</t>
         </is>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>4</v>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
           <t>Square Leg</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -26725,35 +29043,35 @@
           <t>S Langa</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Yorker</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Dig Out</t>
         </is>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>2</v>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
           <t>Third Man</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -26804,35 +29122,35 @@
           <t>S Langa</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>Middle Stump</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>On Drive</t>
         </is>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>1</v>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
           <t>Mid On</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -26883,35 +29201,35 @@
           <t>T Ntini</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>Middle Stump</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Yorker</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Dig Out</t>
         </is>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>1</v>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
           <t>Mid On</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -26962,35 +29280,35 @@
           <t>T Ntini</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>Middle Stump</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Yorker</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Dig Out</t>
         </is>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>2</v>
       </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
           <t>Mid On</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -27041,35 +29359,35 @@
           <t>T Ntini</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Yorker</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Dig Out</t>
         </is>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>2</v>
       </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
           <t>Mid On</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -27120,35 +29438,35 @@
           <t>T Ntini</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>Wide</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Lofted Cover Drive</t>
         </is>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>6</v>
       </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
           <t>Cover</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -27199,35 +29517,35 @@
           <t>S Langa</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>Outside Leg</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Yorker</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Dig Out</t>
         </is>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>1</v>
       </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
           <t>Mid On</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -27278,35 +29596,35 @@
           <t>S Langa</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>Leg Stump</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>On Drive</t>
         </is>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>1</v>
       </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
           <t>Mid On</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -27357,35 +29675,35 @@
           <t>T Ntini</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>Wide</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Hack</t>
         </is>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>1</v>
       </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
           <t>Fine Leg</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -27436,35 +29754,35 @@
           <t>T Ntini</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>Leg Stump</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Lofted On Drive</t>
         </is>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>6</v>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
           <t>Mid On</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -27515,35 +29833,35 @@
           <t>T Ntini</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>Wide</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Yorker</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Scoop</t>
         </is>
       </c>
-      <c r="N34" t="n">
+      <c r="O34" t="n">
         <v>1</v>
       </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
           <t>Square Leg</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -27594,35 +29912,35 @@
           <t>N Smith</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>Leg Stump</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Leg Glance</t>
         </is>
       </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
         <v>4</v>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>Leg Byes</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>Fine Leg</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -27673,35 +29991,35 @@
           <t>Z Foulkes</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>Leg Stump</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Back Foot Flick</t>
         </is>
       </c>
-      <c r="N36" t="n">
+      <c r="O36" t="n">
         <v>2</v>
       </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
           <t>Square Leg</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -27752,35 +30070,35 @@
           <t>Z Foulkes</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Forward Defence</t>
         </is>
       </c>
-      <c r="N37" t="n">
+      <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -27831,35 +30149,35 @@
           <t>Z Foulkes</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>Middle Stump</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Pull</t>
         </is>
       </c>
-      <c r="N38" t="n">
+      <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -27910,35 +30228,35 @@
           <t>Z Foulkes</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>Middle Stump</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Back Foot Defense</t>
         </is>
       </c>
-      <c r="N39" t="n">
+      <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -27989,35 +30307,35 @@
           <t>N Smith</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>Off Stump</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Forward Defence</t>
         </is>
       </c>
-      <c r="N40" t="n">
+      <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -28068,35 +30386,35 @@
           <t>N Smith</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>Leg Stump</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Leg Glance</t>
         </is>
       </c>
-      <c r="N41" t="n">
+      <c r="O41" t="n">
         <v>1</v>
       </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
           <t>Fine Leg</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -28147,37 +30465,37 @@
           <t>B Tickner</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>Middle Stump</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>Pull</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>Wicket</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>Caught</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>Square Leg</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -28228,35 +30546,35 @@
           <t>B Tickner</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>Off Stump</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>Forward Defence</t>
         </is>
       </c>
-      <c r="N43" t="n">
+      <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -28307,35 +30625,35 @@
           <t>B Tickner</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>Forward Defence</t>
         </is>
       </c>
-      <c r="N44" t="n">
+      <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -28386,35 +30704,35 @@
           <t>B Tickner</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>Yorker</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>Forward Defence</t>
         </is>
       </c>
-      <c r="N45" t="n">
+      <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -28465,35 +30783,35 @@
           <t>B Tickner</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>Cover Drive</t>
         </is>
       </c>
-      <c r="N46" t="n">
+      <c r="O46" t="n">
         <v>1</v>
       </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
           <t>Fine Leg</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -28544,35 +30862,35 @@
           <t>N Smith</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>Middle Stump</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>Forward Defence</t>
         </is>
       </c>
-      <c r="N47" t="n">
+      <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -28623,35 +30941,35 @@
           <t>N Smith</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>Back Foot Punch</t>
         </is>
       </c>
-      <c r="N48" t="n">
+      <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -28702,35 +31020,35 @@
           <t>N Smith</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>Middle Stump</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>Back Foot Defense</t>
         </is>
       </c>
-      <c r="N49" t="n">
+      <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -28781,35 +31099,35 @@
           <t>N Smith</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>Forward Defence</t>
         </is>
       </c>
-      <c r="N50" t="n">
+      <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -28860,35 +31178,35 @@
           <t>N Smith</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>Leg Stump</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>Forward Defence</t>
         </is>
       </c>
-      <c r="N51" t="n">
+      <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
@@ -28939,35 +31257,35 @@
           <t>N Smith</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>Middle Stump</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>Forward Defence</t>
         </is>
       </c>
-      <c r="N52" t="n">
+      <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
         <is>
           <t>Edge</t>
         </is>
@@ -29018,35 +31336,35 @@
           <t>B Tickner</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>Middle Stump</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>Forward Defence</t>
         </is>
       </c>
-      <c r="N53" t="n">
+      <c r="O53" t="n">
         <v>4</v>
       </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
           <t>Third Man</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>Edge</t>
         </is>
@@ -29097,35 +31415,35 @@
           <t>N Smith</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>Forward Defence</t>
         </is>
       </c>
-      <c r="N54" t="n">
+      <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
         <is>
           <t>Edge</t>
         </is>
@@ -29176,37 +31494,37 @@
           <t>N Smith</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>Forward Defence</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>Wicket</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>Caught</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t xml:space="preserve">2nd Slip </t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>Edge</t>
         </is>
@@ -29257,35 +31575,35 @@
           <t>H Coetzer</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>Wide</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="N56" t="n">
+      <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
@@ -29336,35 +31654,35 @@
           <t>N Smith</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="N57" t="n">
+      <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
@@ -29415,35 +31733,35 @@
           <t>B Tickner</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>Outside Leg</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="N58" t="n">
+      <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
@@ -29494,35 +31812,35 @@
           <t>B Tickner</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="N59" t="n">
+      <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
@@ -29573,35 +31891,35 @@
           <t>B Tickner</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="N60" t="n">
+      <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
@@ -29652,35 +31970,35 @@
           <t>B Tickner</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>Leg Stump</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="N61" t="n">
+      <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
@@ -29731,35 +32049,35 @@
           <t>B Tickner</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>Leg Stump</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="N62" t="n">
+      <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
@@ -29810,35 +32128,35 @@
           <t>B Tickner</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>Leg Stump</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="N63" t="n">
+      <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
@@ -29889,35 +32207,35 @@
           <t>B Tickner</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>Leg Stump</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="N64" t="n">
+      <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
@@ -29968,35 +32286,35 @@
           <t>B Tickner</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>Leg Stump</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="N65" t="n">
+      <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
@@ -30047,35 +32365,35 @@
           <t>B Tickner</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="N66" t="n">
+      <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
@@ -30126,35 +32444,35 @@
           <t>N Smith</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="N67" t="n">
+      <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
@@ -30205,35 +32523,35 @@
           <t>N Smith</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="N68" t="n">
+      <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
@@ -30284,35 +32602,35 @@
           <t>N Smith</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>Outside Leg</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="N69" t="n">
+      <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
@@ -30363,35 +32681,35 @@
           <t>N Smith</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
-      <c r="N70" t="n">
+      <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
@@ -30442,35 +32760,35 @@
           <t>H Coetzer</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>Back Foot Punch</t>
         </is>
       </c>
-      <c r="N71" t="n">
+      <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
         <is>
           <t>Miss</t>
         </is>
@@ -30521,35 +32839,35 @@
           <t>S Langa</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>Pull</t>
         </is>
       </c>
-      <c r="N72" t="n">
+      <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
         <is>
           <t>Miss</t>
         </is>
@@ -30600,35 +32918,35 @@
           <t>N Smith</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>Outside Leg</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>Back Foot Flick</t>
         </is>
       </c>
-      <c r="N73" t="n">
+      <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
         <is>
           <t>Miss</t>
         </is>
@@ -30679,35 +32997,35 @@
           <t>N Smith</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>Outside Leg</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>Pull</t>
         </is>
       </c>
-      <c r="N74" t="n">
+      <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
         <is>
           <t>Miss</t>
         </is>
@@ -30758,32 +33076,32 @@
           <t>S Kaber</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>Straight Drive</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>Wicket</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>Stumped</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="R75" t="inlineStr">
         <is>
           <t>Miss</t>
         </is>
@@ -30834,30 +33152,30 @@
           <t>T Luus</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>Wide</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>Cut</t>
         </is>
       </c>
-      <c r="N76" t="n">
+      <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr">
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
         <is>
           <t>Miss</t>
         </is>
@@ -30908,34 +33226,1416 @@
           <t>T Luus</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>Leg Stump</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>Flick</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>Wicket</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>LBW</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="R77" t="inlineStr">
         <is>
           <t>Miss</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>8</v>
+      </c>
+      <c r="I78" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>L Alder</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Middle Stump</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Front Foot Defense</t>
+        </is>
+      </c>
+      <c r="O78" t="n">
+        <v>1</v>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Mid Wicket</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>8</v>
+      </c>
+      <c r="I79" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>L Alder</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Front Foot Defense</t>
+        </is>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>8</v>
+      </c>
+      <c r="I80" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>L Alder</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Middle Stump</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Back Foot Defense</t>
+        </is>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>8</v>
+      </c>
+      <c r="I81" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>E Kitshini</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Cut</t>
+        </is>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>8</v>
+      </c>
+      <c r="I82" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>E Kitshini</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Cut</t>
+        </is>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>8</v>
+      </c>
+      <c r="I83" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>E Kitshini</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Middle Stump</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Yorker</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Cover Drive</t>
+        </is>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>8</v>
+      </c>
+      <c r="I84" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>E Kitshini</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Off Stump</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Back Foot Punch</t>
+        </is>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>8</v>
+      </c>
+      <c r="I85" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>E Kitshini</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Leg Stump</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Yorker</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Dig Out</t>
+        </is>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>8</v>
+      </c>
+      <c r="I86" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>L Sadler</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Yorker</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Dig Out</t>
+        </is>
+      </c>
+      <c r="O86" t="n">
+        <v>1</v>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>8</v>
+      </c>
+      <c r="I87" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>L Sadler</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Off Stump</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Yorker</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Dig Out</t>
+        </is>
+      </c>
+      <c r="O87" t="n">
+        <v>2</v>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Mid On</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>8</v>
+      </c>
+      <c r="I88" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>L Sadler</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Full Toss</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>On Drive</t>
+        </is>
+      </c>
+      <c r="O88" t="n">
+        <v>1</v>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>Mid On</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>8</v>
+      </c>
+      <c r="I89" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>B Cele</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Off Stump</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Lofted On Drive</t>
+        </is>
+      </c>
+      <c r="O89" t="n">
+        <v>6</v>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>Mid On</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>8</v>
+      </c>
+      <c r="I90" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>B Cele</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Wide</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Cut</t>
+        </is>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>8</v>
+      </c>
+      <c r="I91" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>L Sadler</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Yorker</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>On Drive</t>
+        </is>
+      </c>
+      <c r="O91" t="n">
+        <v>4</v>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>Mid On</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>8</v>
+      </c>
+      <c r="I92" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>L Sadler</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Wide</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Yorker</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Dig Out</t>
+        </is>
+      </c>
+      <c r="O92" t="n">
+        <v>1</v>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Extra Cover</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>8</v>
+      </c>
+      <c r="I93" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>L Sadler</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Leg Stump</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Full Toss</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Flick</t>
+        </is>
+      </c>
+      <c r="O93" t="n">
+        <v>1</v>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>Mid Wicket</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>8</v>
+      </c>
+      <c r="I94" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>L Sadler</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Wide</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="O94" t="n">
+        <v>6</v>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>Mid Wicket</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>YesPlay Pro20 Cup</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Limpopo Impalas</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Garden Route Badgers</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Polokwane</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>8</v>
+      </c>
+      <c r="I95" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>B Cele</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Wide</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="O95" t="n">
+        <v>1</v>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>Mid Wicket</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>Edge</t>
         </is>
       </c>
     </row>

--- a/backend/data/raw/Mayes_Bowling_Batting.xlsx
+++ b/backend/data/raw/Mayes_Bowling_Batting.xlsx
@@ -27305,6 +27305,11 @@
           <t>H Coetzer</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Right Arm Medium</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>Off Stump</t>
@@ -27384,6 +27389,11 @@
           <t>A Mhletywa</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>Outside Leg</t>
@@ -27463,6 +27473,11 @@
           <t>A Mhletywa</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>Outside Leg</t>
@@ -27542,6 +27557,11 @@
           <t>H Coetzer</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Right Arm Medium</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>Off Stump</t>
@@ -27621,6 +27641,11 @@
           <t>A Mhletywa</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>Leg Stump</t>
@@ -27700,6 +27725,11 @@
           <t>A Mhletywa</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>Middle Stump</t>
@@ -27779,6 +27809,11 @@
           <t>A Mhletywa</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>Leg Stump</t>
@@ -27858,6 +27893,11 @@
           <t>A Mhletywa</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>Middle Stump</t>
@@ -27937,6 +27977,11 @@
           <t>S Langa</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Right Arm Medium</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>Leg Stump</t>
@@ -28016,6 +28061,11 @@
           <t>S Langa</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Right Arm Medium</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>Leg Stump</t>
@@ -28095,6 +28145,11 @@
           <t>S Langa</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Right Arm Medium</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -28174,6 +28229,11 @@
           <t>S Langa</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Right Arm Medium</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -28253,6 +28313,11 @@
           <t>A Mhletywa</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -28332,6 +28397,11 @@
           <t>A Mhletywa</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>Leg Stump</t>
@@ -28411,6 +28481,11 @@
           <t>A Mhletywa</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -28490,6 +28565,11 @@
           <t>S Langa</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Right Arm Medium</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>Leg Stump</t>
@@ -28569,6 +28649,11 @@
           <t>S Langa</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Right Arm Medium</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>Off Stump</t>
@@ -28648,6 +28733,11 @@
           <t>S Langa</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Right Arm Medium</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>Outside Leg</t>
@@ -28727,6 +28817,11 @@
           <t>S Langa</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Right Arm Medium</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>Wide</t>
@@ -28806,6 +28901,11 @@
           <t>T Ntini</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -28885,6 +28985,11 @@
           <t>T Ntini</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>Middle Stump</t>
@@ -28964,6 +29069,11 @@
           <t>S Langa</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Right Arm Medium</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>Outside Leg</t>
@@ -29043,6 +29153,11 @@
           <t>S Langa</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Right Arm Medium</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -29122,6 +29237,11 @@
           <t>S Langa</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Right Arm Medium</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>Middle Stump</t>
@@ -29201,6 +29321,11 @@
           <t>T Ntini</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>Middle Stump</t>
@@ -29280,6 +29405,11 @@
           <t>T Ntini</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>Middle Stump</t>
@@ -29359,6 +29489,11 @@
           <t>T Ntini</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -29438,6 +29573,11 @@
           <t>T Ntini</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>Wide</t>
@@ -29517,6 +29657,11 @@
           <t>S Langa</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Right Arm Medium</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>Outside Leg</t>
@@ -29596,6 +29741,11 @@
           <t>S Langa</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Right Arm Medium</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>Leg Stump</t>
@@ -29675,6 +29825,11 @@
           <t>T Ntini</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>Wide</t>
@@ -29754,6 +29909,11 @@
           <t>T Ntini</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>Leg Stump</t>
@@ -29833,6 +29993,11 @@
           <t>T Ntini</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>Wide</t>
@@ -29912,6 +30077,11 @@
           <t>N Smith</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>Leg Stump</t>
@@ -29991,6 +30161,11 @@
           <t>Z Foulkes</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>Leg Stump</t>
@@ -30070,6 +30245,11 @@
           <t>Z Foulkes</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -30149,6 +30329,11 @@
           <t>Z Foulkes</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>Middle Stump</t>
@@ -30228,6 +30413,11 @@
           <t>Z Foulkes</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>Middle Stump</t>
@@ -30307,6 +30497,11 @@
           <t>N Smith</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>Off Stump</t>
@@ -30386,6 +30581,11 @@
           <t>N Smith</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>Leg Stump</t>
@@ -30465,6 +30665,11 @@
           <t>B Tickner</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>Middle Stump</t>
@@ -30546,6 +30751,11 @@
           <t>B Tickner</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>Off Stump</t>
@@ -30625,6 +30835,11 @@
           <t>B Tickner</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -30704,6 +30919,11 @@
           <t>B Tickner</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -30783,6 +31003,11 @@
           <t>B Tickner</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -30862,6 +31087,11 @@
           <t>N Smith</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>Middle Stump</t>
@@ -30941,6 +31171,11 @@
           <t>N Smith</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -31020,6 +31255,11 @@
           <t>N Smith</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>Middle Stump</t>
@@ -31099,6 +31339,11 @@
           <t>N Smith</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -31178,6 +31423,11 @@
           <t>N Smith</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>Leg Stump</t>
@@ -31257,6 +31507,11 @@
           <t>N Smith</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>Middle Stump</t>
@@ -31336,6 +31591,11 @@
           <t>B Tickner</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>Middle Stump</t>
@@ -31415,6 +31675,11 @@
           <t>N Smith</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -31494,6 +31759,11 @@
           <t>N Smith</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -31575,6 +31845,11 @@
           <t>H Coetzer</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Right Arm Medium</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>Wide</t>
@@ -31654,6 +31929,11 @@
           <t>N Smith</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -31733,6 +32013,11 @@
           <t>B Tickner</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>Outside Leg</t>
@@ -31812,6 +32097,11 @@
           <t>B Tickner</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -31891,6 +32181,11 @@
           <t>B Tickner</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -31970,6 +32265,11 @@
           <t>B Tickner</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>Leg Stump</t>
@@ -32049,6 +32349,11 @@
           <t>B Tickner</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>Leg Stump</t>
@@ -32128,6 +32433,11 @@
           <t>B Tickner</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>Leg Stump</t>
@@ -32207,6 +32517,11 @@
           <t>B Tickner</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>Leg Stump</t>
@@ -32286,6 +32601,11 @@
           <t>B Tickner</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>Leg Stump</t>
@@ -32365,6 +32685,11 @@
           <t>B Tickner</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -32444,6 +32769,11 @@
           <t>N Smith</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -32523,6 +32853,11 @@
           <t>N Smith</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -32602,6 +32937,11 @@
           <t>N Smith</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>Outside Leg</t>
@@ -32681,6 +33021,11 @@
           <t>N Smith</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -32760,6 +33105,11 @@
           <t>H Coetzer</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Right Arm Medium</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -32839,6 +33189,11 @@
           <t>S Langa</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Right Arm Medium</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -32918,6 +33273,11 @@
           <t>N Smith</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>Outside Leg</t>
@@ -32997,6 +33357,11 @@
           <t>N Smith</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>Outside Leg</t>
@@ -33076,6 +33441,11 @@
           <t>S Kaber</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Left Arm Wrist Spin</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -33152,6 +33522,11 @@
           <t>T Luus</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>Wide</t>
@@ -33226,6 +33601,11 @@
           <t>T Luus</t>
         </is>
       </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>Leg Stump</t>
@@ -33302,6 +33682,11 @@
           <t>L Alder</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Left Arm Finger Spin</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>Middle Stump</t>
@@ -33381,6 +33766,11 @@
           <t>L Alder</t>
         </is>
       </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Left Arm Finger Spin</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -33455,6 +33845,11 @@
           <t>L Alder</t>
         </is>
       </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Left Arm Finger Spin</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>Middle Stump</t>
@@ -33529,6 +33924,11 @@
           <t>E Kitshini</t>
         </is>
       </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Left Arm Finger Spin</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -33603,6 +34003,11 @@
           <t>E Kitshini</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Left Arm Finger Spin</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -33677,6 +34082,11 @@
           <t>E Kitshini</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Left Arm Finger Spin</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>Middle Stump</t>
@@ -33751,6 +34161,11 @@
           <t>E Kitshini</t>
         </is>
       </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Left Arm Finger Spin</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>Off Stump</t>
@@ -33825,6 +34240,11 @@
           <t>E Kitshini</t>
         </is>
       </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Left Arm Finger Spin</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>Leg Stump</t>
@@ -33899,6 +34319,11 @@
           <t>L Sadler</t>
         </is>
       </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -33978,6 +34403,11 @@
           <t>L Sadler</t>
         </is>
       </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>Off Stump</t>
@@ -34057,6 +34487,11 @@
           <t>L Sadler</t>
         </is>
       </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -34136,6 +34571,11 @@
           <t>B Cele</t>
         </is>
       </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Right Arm Medium</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>Off Stump</t>
@@ -34215,6 +34655,11 @@
           <t>B Cele</t>
         </is>
       </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Right Arm Medium</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>Wide</t>
@@ -34289,6 +34734,11 @@
           <t>L Sadler</t>
         </is>
       </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -34368,6 +34818,11 @@
           <t>L Sadler</t>
         </is>
       </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>Wide</t>
@@ -34447,6 +34902,11 @@
           <t>L Sadler</t>
         </is>
       </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>Leg Stump</t>
@@ -34526,6 +34986,11 @@
           <t>L Sadler</t>
         </is>
       </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Right Arm Fast</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>Wide</t>
@@ -34603,6 +35068,11 @@
       <c r="J95" t="inlineStr">
         <is>
           <t>B Cele</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Right Arm Medium</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">

--- a/backend/data/raw/Mayes_Bowling_Batting.xlsx
+++ b/backend/data/raw/Mayes_Bowling_Batting.xlsx
@@ -24545,6 +24545,11 @@
           <t>Edge</t>
         </is>
       </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>Caught at Keeper</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
